--- a/examples/medibec/deliverables/MediBec_Scenario_Selection.xlsx
+++ b/examples/medibec/deliverables/MediBec_Scenario_Selection.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
@@ -2292,7 +2292,7 @@
     <t xml:space="preserve">Very frequent human error; limited individual impact; privacy register obligations.</t>
   </si>
   <si>
-    <t xml:space="preserve">Evidence gap - telehealth use</t>
+    <t xml:space="preserve">Information gap - telehealth use</t>
   </si>
   <si>
     <t xml:space="preserve">Telehealth use not documented; limited consequence.</t>
@@ -3153,7 +3153,7 @@
     <t xml:space="preserve">Section D / Instruction s.19 - Preparation for quantitative analysis</t>
   </si>
   <si>
-    <t xml:space="preserve">Preliminary values are taken from the constituent scenarios of the 30-scenario assessment: anchor = lead constituent (core causal chain); range = min-max across constituents. Analyst estimates - validation required.</t>
+    <t xml:space="preserve">Preliminary values are taken from the constituent scenarios of the 30-scenario assessment: anchor = lead constituent (core causal chain); range = min-max across constituents. Analytical estimates — validation required.</t>
   </si>
   <si>
     <t xml:space="preserve">Constituents</t>
@@ -3282,7 +3282,7 @@
     <t xml:space="preserve">0.85-0.95</t>
   </si>
   <si>
-    <t xml:space="preserve">Limited for S8; anchor CVSS-B 9.4</t>
+    <t xml:space="preserve">Limited for S8; anchor CVSS-B 9.3</t>
   </si>
   <si>
     <t xml:space="preserve">Very high</t>
@@ -4014,7 +4014,7 @@
     <t xml:space="preserve">New in the 10-scenario portfolio: P09 hub single point of failure (S16) and P10 staff disclosure via AI and misdirected communications (S26, S21).</t>
   </si>
   <si>
-    <t xml:space="preserve">Implication: the CRG KRIs, treatment portfolio and budget were computed on S1-S30 and remain usable; re-quantify P01-P10 as whole scenarios before presenting a 10-scenario register to management.</t>
+    <t xml:space="preserve">Implication: the CRG risk indices, treatment portfolio and budget were computed on S1-S30 and remain usable; re-quantify P01-P10 as whole scenarios before presenting a 10-scenario register to management.</t>
   </si>
 </sst>
 </file>
